--- a/test_data/excel.xlsx
+++ b/test_data/excel.xlsx
@@ -953,11 +953,11 @@
       </s:c>
       <s:c r="D9" s="5" t="inlineStr">
         <s:is>
-          <s:t>Armani</s:t>
+          <s:t>Nike</s:t>
         </s:is>
       </s:c>
       <s:c r="E9" s="9">
-        <s:v>100</s:v>
+        <s:v>450</s:v>
       </s:c>
     </s:row>
     <s:row r="10" spans="2:5">
@@ -971,11 +971,11 @@
       </s:c>
       <s:c r="D10" s="5" t="inlineStr">
         <s:is>
-          <s:t>Nike</s:t>
+          <s:t>Puma</s:t>
         </s:is>
       </s:c>
       <s:c r="E10" s="9">
-        <s:v>6000</s:v>
+        <s:v>320</s:v>
       </s:c>
     </s:row>
     <s:row r="11" spans="2:5">
@@ -989,11 +989,11 @@
       </s:c>
       <s:c r="D11" s="5" t="inlineStr">
         <s:is>
-          <s:t>Nike</s:t>
+          <s:t>Asics</s:t>
         </s:is>
       </s:c>
       <s:c r="E11" s="9">
-        <s:v>450</s:v>
+        <s:v>200</s:v>
       </s:c>
     </s:row>
     <s:row r="12" spans="2:5">
@@ -1007,11 +1007,11 @@
       </s:c>
       <s:c r="D12" s="5" t="inlineStr">
         <s:is>
-          <s:t>Puma</s:t>
+          <s:t>Asics</s:t>
         </s:is>
       </s:c>
       <s:c r="E12" s="9">
-        <s:v>320</s:v>
+        <s:v>200</s:v>
       </s:c>
     </s:row>
     <s:row r="13" spans="2:5">
@@ -1025,11 +1025,11 @@
       </s:c>
       <s:c r="D13" s="5" t="inlineStr">
         <s:is>
-          <s:t>Asics</s:t>
+          <s:t>Puma</s:t>
         </s:is>
       </s:c>
       <s:c r="E13" s="9">
-        <s:v>200</s:v>
+        <s:v>999</s:v>
       </s:c>
     </s:row>
     <s:row r="14" spans="2:5">
@@ -1043,11 +1043,11 @@
       </s:c>
       <s:c r="D14" s="5" t="inlineStr">
         <s:is>
-          <s:t>Asics</s:t>
+          <s:t>Puma</s:t>
         </s:is>
       </s:c>
       <s:c r="E14" s="9">
-        <s:v>200</s:v>
+        <s:v>1000</s:v>
       </s:c>
     </s:row>
     <s:row r="15" spans="2:5">
@@ -1074,12 +1074,12 @@
       </s:c>
       <s:c r="C16" s="5" t="inlineStr">
         <s:is>
-          <s:t>Armani</s:t>
+          <s:t>Steven Michael</s:t>
         </s:is>
       </s:c>
       <s:c r="D16" s="5" t="inlineStr">
         <s:is>
-          <s:t>100</s:t>
+          <s:t>Puma</s:t>
         </s:is>
       </s:c>
       <s:c r="E16" s="9">
@@ -1094,12 +1094,12 @@
       </s:c>
       <s:c r="C17" s="5" t="inlineStr">
         <s:is>
-          <s:t>Nike</s:t>
+          <s:t>100</s:t>
         </s:is>
       </s:c>
       <s:c r="D17" s="5" t="inlineStr">
         <s:is>
-          <s:t>6000</s:t>
+          <s:t>Asics</s:t>
         </s:is>
       </s:c>
       <s:c r="E17" s="9">
@@ -1114,12 +1114,12 @@
       </s:c>
       <s:c r="C18" s="5" t="inlineStr">
         <s:is>
-          <s:t>Nike</s:t>
+          <s:t>6000</s:t>
         </s:is>
       </s:c>
       <s:c r="D18" s="5" t="inlineStr">
         <s:is>
-          <s:t>450</s:t>
+          <s:t>Asics</s:t>
         </s:is>
       </s:c>
       <s:c r="E18" s="9">
@@ -1134,12 +1134,12 @@
       </s:c>
       <s:c r="C19" s="5" t="inlineStr">
         <s:is>
-          <s:t>Puma</s:t>
+          <s:t>450</s:t>
         </s:is>
       </s:c>
       <s:c r="D19" s="5" t="inlineStr">
         <s:is>
-          <s:t>320</s:t>
+          <s:t>450</s:t>
         </s:is>
       </s:c>
       <s:c r="E19" s="9">
@@ -1154,12 +1154,12 @@
       </s:c>
       <s:c r="C20" s="5" t="inlineStr">
         <s:is>
-          <s:t>Asics</s:t>
+          <s:t>320</s:t>
         </s:is>
       </s:c>
       <s:c r="D20" s="5" t="inlineStr">
         <s:is>
-          <s:t>200</s:t>
+          <s:t>320</s:t>
         </s:is>
       </s:c>
       <s:c r="E20" s="9">
@@ -1174,7 +1174,7 @@
       </s:c>
       <s:c r="C21" s="5" t="inlineStr">
         <s:is>
-          <s:t>Asics</s:t>
+          <s:t>200</s:t>
         </s:is>
       </s:c>
       <s:c r="D21" s="5" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </s:c>
       <s:c r="C22" s="5" t="inlineStr">
         <s:is>
-          <s:t>Asics</s:t>
+          <s:t>200</s:t>
         </s:is>
       </s:c>
       <s:c r="D22" s="5" t="inlineStr">
@@ -1207,12 +1207,14 @@
       </s:c>
     </s:row>
     <s:row r="23" spans="2:5">
-      <s:c r="B23" s="5">
-        <s:v>1346</s:v>
+      <s:c r="B23" s="5" t="inlineStr">
+        <s:is>
+          <s:t>Puma</s:t>
+        </s:is>
       </s:c>
       <s:c r="C23" s="5" t="inlineStr">
         <s:is>
-          <s:t>Puma</s:t>
+          <s:t>999</s:t>
         </s:is>
       </s:c>
       <s:c r="D23" s="5" t="inlineStr">

--- a/test_data/excel.xlsx
+++ b/test_data/excel.xlsx
@@ -1094,12 +1094,12 @@
       </s:c>
       <s:c r="C17" s="5" t="inlineStr">
         <s:is>
-          <s:t>100</s:t>
+          <s:t>Puma</s:t>
         </s:is>
       </s:c>
       <s:c r="D17" s="5" t="inlineStr">
         <s:is>
-          <s:t>Asics</s:t>
+          <s:t>320</s:t>
         </s:is>
       </s:c>
       <s:c r="E17" s="9">
@@ -1114,12 +1114,12 @@
       </s:c>
       <s:c r="C18" s="5" t="inlineStr">
         <s:is>
-          <s:t>6000</s:t>
+          <s:t>Asics</s:t>
         </s:is>
       </s:c>
       <s:c r="D18" s="5" t="inlineStr">
         <s:is>
-          <s:t>Asics</s:t>
+          <s:t>200</s:t>
         </s:is>
       </s:c>
       <s:c r="E18" s="9">
@@ -1134,12 +1134,12 @@
       </s:c>
       <s:c r="C19" s="5" t="inlineStr">
         <s:is>
-          <s:t>450</s:t>
+          <s:t>Asics</s:t>
         </s:is>
       </s:c>
       <s:c r="D19" s="5" t="inlineStr">
         <s:is>
-          <s:t>450</s:t>
+          <s:t>200</s:t>
         </s:is>
       </s:c>
       <s:c r="E19" s="9">
@@ -1154,12 +1154,12 @@
       </s:c>
       <s:c r="C20" s="5" t="inlineStr">
         <s:is>
-          <s:t>320</s:t>
+          <s:t>Puma</s:t>
         </s:is>
       </s:c>
       <s:c r="D20" s="5" t="inlineStr">
         <s:is>
-          <s:t>320</s:t>
+          <s:t>999</s:t>
         </s:is>
       </s:c>
       <s:c r="E20" s="9">
@@ -1174,7 +1174,7 @@
       </s:c>
       <s:c r="C21" s="5" t="inlineStr">
         <s:is>
-          <s:t>200</s:t>
+          <s:t>Asics</s:t>
         </s:is>
       </s:c>
       <s:c r="D21" s="5" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </s:c>
       <s:c r="C22" s="5" t="inlineStr">
         <s:is>
-          <s:t>200</s:t>
+          <s:t>Asics</s:t>
         </s:is>
       </s:c>
       <s:c r="D22" s="5" t="inlineStr">
@@ -1207,14 +1207,12 @@
       </s:c>
     </s:row>
     <s:row r="23" spans="2:5">
-      <s:c r="B23" s="5" t="inlineStr">
+      <s:c r="B23" s="5">
+        <s:v>1346</s:v>
+      </s:c>
+      <s:c r="C23" s="5" t="inlineStr">
         <s:is>
           <s:t>Puma</s:t>
-        </s:is>
-      </s:c>
-      <s:c r="C23" s="5" t="inlineStr">
-        <s:is>
-          <s:t>999</s:t>
         </s:is>
       </s:c>
       <s:c r="D23" s="5" t="inlineStr">

--- a/test_data/excel.xlsx
+++ b/test_data/excel.xlsx
@@ -1087,19 +1087,17 @@
       </s:c>
     </s:row>
     <s:row r="17" spans="2:5">
-      <s:c r="B17" s="5" t="inlineStr">
-        <s:is>
-          <s:t>Armani</s:t>
-        </s:is>
+      <s:c r="B17" s="5">
+        <s:v>1328</s:v>
       </s:c>
       <s:c r="C17" s="5" t="inlineStr">
         <s:is>
-          <s:t>Puma</s:t>
+          <s:t>Nike</s:t>
         </s:is>
       </s:c>
       <s:c r="D17" s="5" t="inlineStr">
         <s:is>
-          <s:t>320</s:t>
+          <s:t>450</s:t>
         </s:is>
       </s:c>
       <s:c r="E17" s="9">
@@ -1107,19 +1105,17 @@
       </s:c>
     </s:row>
     <s:row r="18" spans="2:5">
-      <s:c r="B18" s="5" t="inlineStr">
-        <s:is>
-          <s:t>Nike</s:t>
-        </s:is>
+      <s:c r="B18" s="5">
+        <s:v>1331</s:v>
       </s:c>
       <s:c r="C18" s="5" t="inlineStr">
         <s:is>
-          <s:t>Asics</s:t>
+          <s:t>Puma</s:t>
         </s:is>
       </s:c>
       <s:c r="D18" s="5" t="inlineStr">
         <s:is>
-          <s:t>200</s:t>
+          <s:t>320</s:t>
         </s:is>
       </s:c>
       <s:c r="E18" s="9">
@@ -1127,19 +1123,17 @@
       </s:c>
     </s:row>
     <s:row r="19" spans="2:5">
-      <s:c r="B19" s="5" t="inlineStr">
+      <s:c r="B19" s="5">
+        <s:v>1334</s:v>
+      </s:c>
+      <s:c r="C19" s="5" t="inlineStr">
         <s:is>
           <s:t>Nike</s:t>
         </s:is>
       </s:c>
-      <s:c r="C19" s="5" t="inlineStr">
-        <s:is>
-          <s:t>Asics</s:t>
-        </s:is>
-      </s:c>
       <s:c r="D19" s="5" t="inlineStr">
         <s:is>
-          <s:t>200</s:t>
+          <s:t>450</s:t>
         </s:is>
       </s:c>
       <s:c r="E19" s="9">
@@ -1147,19 +1141,17 @@
       </s:c>
     </s:row>
     <s:row r="20" spans="2:5">
-      <s:c r="B20" s="5" t="inlineStr">
+      <s:c r="B20" s="5">
+        <s:v>1337</s:v>
+      </s:c>
+      <s:c r="C20" s="5" t="inlineStr">
         <s:is>
           <s:t>Puma</s:t>
         </s:is>
       </s:c>
-      <s:c r="C20" s="5" t="inlineStr">
-        <s:is>
-          <s:t>Puma</s:t>
-        </s:is>
-      </s:c>
       <s:c r="D20" s="5" t="inlineStr">
         <s:is>
-          <s:t>999</s:t>
+          <s:t>320</s:t>
         </s:is>
       </s:c>
       <s:c r="E20" s="9">
@@ -1167,10 +1159,8 @@
       </s:c>
     </s:row>
     <s:row r="21" spans="2:5">
-      <s:c r="B21" s="5" t="inlineStr">
-        <s:is>
-          <s:t>Asics</s:t>
-        </s:is>
+      <s:c r="B21" s="5">
+        <s:v>1340</s:v>
       </s:c>
       <s:c r="C21" s="5" t="inlineStr">
         <s:is>
@@ -1187,10 +1177,8 @@
       </s:c>
     </s:row>
     <s:row r="22" spans="2:5">
-      <s:c r="B22" s="5" t="inlineStr">
-        <s:is>
-          <s:t>Asics</s:t>
-        </s:is>
+      <s:c r="B22" s="5">
+        <s:v>1343</s:v>
       </s:c>
       <s:c r="C22" s="5" t="inlineStr">
         <s:is>
@@ -1212,12 +1200,12 @@
       </s:c>
       <s:c r="C23" s="5" t="inlineStr">
         <s:is>
-          <s:t>Puma</s:t>
+          <s:t>Bruce Rich</s:t>
         </s:is>
       </s:c>
       <s:c r="D23" s="5" t="inlineStr">
         <s:is>
-          <s:t>999</s:t>
+          <s:t>Nike</s:t>
         </s:is>
       </s:c>
       <s:c r="E23" s="9">
